--- a/docs/payment-schedule-templates/Payment Schedules - Customer Portal/Collection_Schedule_Template_36mo.xlsx
+++ b/docs/payment-schedule-templates/Payment Schedules - Customer Portal/Collection_Schedule_Template_36mo.xlsx
@@ -1067,20 +1067,55 @@
       </c>
     </row>
     <row r="2" ht="15" customHeight="1" s="14">
-      <c r="A2" s="20" t="n"/>
-      <c r="B2" s="20" t="n"/>
-      <c r="C2" s="20" t="n"/>
-      <c r="D2" s="20" t="n"/>
-      <c r="E2" s="20" t="n"/>
-      <c r="F2" s="20" t="n"/>
-      <c r="G2" s="21" t="n"/>
-      <c r="H2" s="21" t="n"/>
-      <c r="I2" s="21" t="n"/>
+      <c r="A2" s="20" t="inlineStr">
+        <is>
+          <t>{{########}}</t>
+        </is>
+      </c>
+      <c r="B2" s="20" t="inlineStr">
+        <is>
+          <t>Alex</t>
+        </is>
+      </c>
+      <c r="C2" s="20" t="inlineStr">
+        <is>
+          <t>Nyandoro</t>
+        </is>
+      </c>
+      <c r="D2" s="20" t="inlineStr">
+        <is>
+          <t>+17785808657</t>
+        </is>
+      </c>
+      <c r="E2" s="20" t="inlineStr">
+        <is>
+          <t>alex@michaeltenable.com</t>
+        </is>
+      </c>
+      <c r="F2" s="20" t="inlineStr">
+        <is>
+          <t>Internal Tester</t>
+        </is>
+      </c>
+      <c r="G2" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" s="21" t="n">
+        <v>5000</v>
+      </c>
+      <c r="I2" s="21" t="n">
+        <v>120000</v>
+      </c>
       <c r="J2" s="22" t="n">
         <v>36</v>
       </c>
-      <c r="K2" s="21" t="n"/>
-      <c r="L2" s="23" t="n"/>
+      <c r="K2" s="21">
+        <f>IF(J2=0,"",ROUND((I2-H2)/J2,2))</f>
+        <v/>
+      </c>
+      <c r="L2" s="23" t="n">
+        <v>46147</v>
+      </c>
       <c r="M2" s="21" t="n"/>
       <c r="N2" s="21" t="n"/>
       <c r="O2" s="21" t="n"/>
@@ -1119,15 +1154,15 @@
       <c r="AV2" s="21" t="n"/>
       <c r="AW2" s="21" t="n"/>
       <c r="AX2" s="24">
-        <f>SUM(M2:AV2)</f>
+        <f>H2+SUM(M2:AV2)</f>
         <v/>
       </c>
       <c r="AY2" s="24">
-        <f>I2-AX2</f>
+        <f>I2-H2-SUM(M2:AV2)</f>
         <v/>
       </c>
       <c r="AZ2" s="25">
-        <f>IF(I2=0,"",AX2/I2)</f>
+        <f>IF(I2=0,"",(H2+SUM(M2:AV2))/I2)</f>
         <v/>
       </c>
       <c r="BA2" s="26" t="n"/>
@@ -1192,15 +1227,15 @@
       <c r="AV3" s="21" t="n"/>
       <c r="AW3" s="21" t="n"/>
       <c r="AX3" s="24">
-        <f>SUM(M3:AV3)</f>
+        <f>H3+SUM(M3:AV3)</f>
         <v/>
       </c>
       <c r="AY3" s="24">
-        <f>I3-AX3</f>
+        <f>I3-H3-SUM(M3:AV3)</f>
         <v/>
       </c>
       <c r="AZ3" s="25">
-        <f>IF(I3=0,"",AX3/I3)</f>
+        <f>IF(I3=0,"",(H3+SUM(M3:AV3))/I3)</f>
         <v/>
       </c>
       <c r="BA3" s="26" t="n"/>
@@ -1265,15 +1300,15 @@
       <c r="AV4" s="21" t="n"/>
       <c r="AW4" s="21" t="n"/>
       <c r="AX4" s="24">
-        <f>SUM(M4:AV4)</f>
+        <f>H4+SUM(M4:AV4)</f>
         <v/>
       </c>
       <c r="AY4" s="24">
-        <f>I4-AX4</f>
+        <f>I4-H4-SUM(M4:AV4)</f>
         <v/>
       </c>
       <c r="AZ4" s="25">
-        <f>IF(I4=0,"",AX4/I4)</f>
+        <f>IF(I4=0,"",(H4+SUM(M4:AV4))/I4)</f>
         <v/>
       </c>
       <c r="BA4" s="26" t="n"/>
@@ -1338,15 +1373,15 @@
       <c r="AV5" s="21" t="n"/>
       <c r="AW5" s="21" t="n"/>
       <c r="AX5" s="24">
-        <f>SUM(M5:AV5)</f>
+        <f>H5+SUM(M5:AV5)</f>
         <v/>
       </c>
       <c r="AY5" s="24">
-        <f>I5-AX5</f>
+        <f>I5-H5-SUM(M5:AV5)</f>
         <v/>
       </c>
       <c r="AZ5" s="25">
-        <f>IF(I5=0,"",AX5/I5)</f>
+        <f>IF(I5=0,"",(H5+SUM(M5:AV5))/I5)</f>
         <v/>
       </c>
       <c r="BA5" s="26" t="n"/>
@@ -1411,15 +1446,15 @@
       <c r="AV6" s="21" t="n"/>
       <c r="AW6" s="21" t="n"/>
       <c r="AX6" s="24">
-        <f>SUM(M6:AV6)</f>
+        <f>H6+SUM(M6:AV6)</f>
         <v/>
       </c>
       <c r="AY6" s="24">
-        <f>I6-AX6</f>
+        <f>I6-H6-SUM(M6:AV6)</f>
         <v/>
       </c>
       <c r="AZ6" s="25">
-        <f>IF(I6=0,"",AX6/I6)</f>
+        <f>IF(I6=0,"",(H6+SUM(M6:AV6))/I6)</f>
         <v/>
       </c>
       <c r="BA6" s="26" t="n"/>
@@ -1484,15 +1519,15 @@
       <c r="AV7" s="21" t="n"/>
       <c r="AW7" s="21" t="n"/>
       <c r="AX7" s="24">
-        <f>SUM(M7:AV7)</f>
+        <f>H7+SUM(M7:AV7)</f>
         <v/>
       </c>
       <c r="AY7" s="24">
-        <f>I7-AX7</f>
+        <f>I7-H7-SUM(M7:AV7)</f>
         <v/>
       </c>
       <c r="AZ7" s="25">
-        <f>IF(I7=0,"",AX7/I7)</f>
+        <f>IF(I7=0,"",(H7+SUM(M7:AV7))/I7)</f>
         <v/>
       </c>
       <c r="BA7" s="26" t="n"/>
@@ -1557,15 +1592,15 @@
       <c r="AV8" s="21" t="n"/>
       <c r="AW8" s="21" t="n"/>
       <c r="AX8" s="24">
-        <f>SUM(M8:AV8)</f>
+        <f>H8+SUM(M8:AV8)</f>
         <v/>
       </c>
       <c r="AY8" s="24">
-        <f>I8-AX8</f>
+        <f>I8-H8-SUM(M8:AV8)</f>
         <v/>
       </c>
       <c r="AZ8" s="25">
-        <f>IF(I8=0,"",AX8/I8)</f>
+        <f>IF(I8=0,"",(H8+SUM(M8:AV8))/I8)</f>
         <v/>
       </c>
       <c r="BA8" s="26" t="n"/>
@@ -1630,15 +1665,15 @@
       <c r="AV9" s="21" t="n"/>
       <c r="AW9" s="21" t="n"/>
       <c r="AX9" s="24">
-        <f>SUM(M9:AV9)</f>
+        <f>H9+SUM(M9:AV9)</f>
         <v/>
       </c>
       <c r="AY9" s="24">
-        <f>I9-AX9</f>
+        <f>I9-H9-SUM(M9:AV9)</f>
         <v/>
       </c>
       <c r="AZ9" s="25">
-        <f>IF(I9=0,"",AX9/I9)</f>
+        <f>IF(I9=0,"",(H9+SUM(M9:AV9))/I9)</f>
         <v/>
       </c>
       <c r="BA9" s="26" t="n"/>
@@ -1703,15 +1738,15 @@
       <c r="AV10" s="21" t="n"/>
       <c r="AW10" s="21" t="n"/>
       <c r="AX10" s="24">
-        <f>SUM(M10:AV10)</f>
+        <f>H10+SUM(M10:AV10)</f>
         <v/>
       </c>
       <c r="AY10" s="24">
-        <f>I10-AX10</f>
+        <f>I10-H10-SUM(M10:AV10)</f>
         <v/>
       </c>
       <c r="AZ10" s="25">
-        <f>IF(I10=0,"",AX10/I10)</f>
+        <f>IF(I10=0,"",(H10+SUM(M10:AV10))/I10)</f>
         <v/>
       </c>
       <c r="BA10" s="26" t="n"/>
@@ -1776,15 +1811,15 @@
       <c r="AV11" s="21" t="n"/>
       <c r="AW11" s="21" t="n"/>
       <c r="AX11" s="24">
-        <f>SUM(M11:AV11)</f>
+        <f>H11+SUM(M11:AV11)</f>
         <v/>
       </c>
       <c r="AY11" s="24">
-        <f>I11-AX11</f>
+        <f>I11-H11-SUM(M11:AV11)</f>
         <v/>
       </c>
       <c r="AZ11" s="25">
-        <f>IF(I11=0,"",AX11/I11)</f>
+        <f>IF(I11=0,"",(H11+SUM(M11:AV11))/I11)</f>
         <v/>
       </c>
       <c r="BA11" s="26" t="n"/>
@@ -1849,15 +1884,15 @@
       <c r="AV12" s="21" t="n"/>
       <c r="AW12" s="21" t="n"/>
       <c r="AX12" s="24">
-        <f>SUM(M12:AV12)</f>
+        <f>H12+SUM(M12:AV12)</f>
         <v/>
       </c>
       <c r="AY12" s="24">
-        <f>I12-AX12</f>
+        <f>I12-H12-SUM(M12:AV12)</f>
         <v/>
       </c>
       <c r="AZ12" s="25">
-        <f>IF(I12=0,"",AX12/I12)</f>
+        <f>IF(I12=0,"",(H12+SUM(M12:AV12))/I12)</f>
         <v/>
       </c>
       <c r="BA12" s="26" t="n"/>
@@ -1922,15 +1957,15 @@
       <c r="AV13" s="21" t="n"/>
       <c r="AW13" s="21" t="n"/>
       <c r="AX13" s="24">
-        <f>SUM(M13:AV13)</f>
+        <f>H13+SUM(M13:AV13)</f>
         <v/>
       </c>
       <c r="AY13" s="24">
-        <f>I13-AX13</f>
+        <f>I13-H13-SUM(M13:AV13)</f>
         <v/>
       </c>
       <c r="AZ13" s="25">
-        <f>IF(I13=0,"",AX13/I13)</f>
+        <f>IF(I13=0,"",(H13+SUM(M13:AV13))/I13)</f>
         <v/>
       </c>
       <c r="BA13" s="26" t="n"/>
@@ -1995,15 +2030,15 @@
       <c r="AV14" s="21" t="n"/>
       <c r="AW14" s="21" t="n"/>
       <c r="AX14" s="24">
-        <f>SUM(M14:AV14)</f>
+        <f>H14+SUM(M14:AV14)</f>
         <v/>
       </c>
       <c r="AY14" s="24">
-        <f>I14-AX14</f>
+        <f>I14-H14-SUM(M14:AV14)</f>
         <v/>
       </c>
       <c r="AZ14" s="25">
-        <f>IF(I14=0,"",AX14/I14)</f>
+        <f>IF(I14=0,"",(H14+SUM(M14:AV14))/I14)</f>
         <v/>
       </c>
       <c r="BA14" s="26" t="n"/>
@@ -2068,15 +2103,15 @@
       <c r="AV15" s="21" t="n"/>
       <c r="AW15" s="21" t="n"/>
       <c r="AX15" s="24">
-        <f>SUM(M15:AV15)</f>
+        <f>H15+SUM(M15:AV15)</f>
         <v/>
       </c>
       <c r="AY15" s="24">
-        <f>I15-AX15</f>
+        <f>I15-H15-SUM(M15:AV15)</f>
         <v/>
       </c>
       <c r="AZ15" s="25">
-        <f>IF(I15=0,"",AX15/I15)</f>
+        <f>IF(I15=0,"",(H15+SUM(M15:AV15))/I15)</f>
         <v/>
       </c>
       <c r="BA15" s="26" t="n"/>
@@ -2141,15 +2176,15 @@
       <c r="AV16" s="21" t="n"/>
       <c r="AW16" s="21" t="n"/>
       <c r="AX16" s="24">
-        <f>SUM(M16:AV16)</f>
+        <f>H16+SUM(M16:AV16)</f>
         <v/>
       </c>
       <c r="AY16" s="24">
-        <f>I16-AX16</f>
+        <f>I16-H16-SUM(M16:AV16)</f>
         <v/>
       </c>
       <c r="AZ16" s="25">
-        <f>IF(I16=0,"",AX16/I16)</f>
+        <f>IF(I16=0,"",(H16+SUM(M16:AV16))/I16)</f>
         <v/>
       </c>
       <c r="BA16" s="26" t="n"/>
@@ -2214,15 +2249,15 @@
       <c r="AV17" s="21" t="n"/>
       <c r="AW17" s="21" t="n"/>
       <c r="AX17" s="24">
-        <f>SUM(M17:AV17)</f>
+        <f>H17+SUM(M17:AV17)</f>
         <v/>
       </c>
       <c r="AY17" s="24">
-        <f>I17-AX17</f>
+        <f>I17-H17-SUM(M17:AV17)</f>
         <v/>
       </c>
       <c r="AZ17" s="25">
-        <f>IF(I17=0,"",AX17/I17)</f>
+        <f>IF(I17=0,"",(H17+SUM(M17:AV17))/I17)</f>
         <v/>
       </c>
       <c r="BA17" s="26" t="n"/>
@@ -2287,15 +2322,15 @@
       <c r="AV18" s="21" t="n"/>
       <c r="AW18" s="21" t="n"/>
       <c r="AX18" s="24">
-        <f>SUM(M18:AV18)</f>
+        <f>H18+SUM(M18:AV18)</f>
         <v/>
       </c>
       <c r="AY18" s="24">
-        <f>I18-AX18</f>
+        <f>I18-H18-SUM(M18:AV18)</f>
         <v/>
       </c>
       <c r="AZ18" s="25">
-        <f>IF(I18=0,"",AX18/I18)</f>
+        <f>IF(I18=0,"",(H18+SUM(M18:AV18))/I18)</f>
         <v/>
       </c>
       <c r="BA18" s="26" t="n"/>
@@ -2360,15 +2395,15 @@
       <c r="AV19" s="21" t="n"/>
       <c r="AW19" s="21" t="n"/>
       <c r="AX19" s="24">
-        <f>SUM(M19:AV19)</f>
+        <f>H19+SUM(M19:AV19)</f>
         <v/>
       </c>
       <c r="AY19" s="24">
-        <f>I19-AX19</f>
+        <f>I19-H19-SUM(M19:AV19)</f>
         <v/>
       </c>
       <c r="AZ19" s="25">
-        <f>IF(I19=0,"",AX19/I19)</f>
+        <f>IF(I19=0,"",(H19+SUM(M19:AV19))/I19)</f>
         <v/>
       </c>
       <c r="BA19" s="26" t="n"/>
@@ -2433,15 +2468,15 @@
       <c r="AV20" s="21" t="n"/>
       <c r="AW20" s="21" t="n"/>
       <c r="AX20" s="24">
-        <f>SUM(M20:AV20)</f>
+        <f>H20+SUM(M20:AV20)</f>
         <v/>
       </c>
       <c r="AY20" s="24">
-        <f>I20-AX20</f>
+        <f>I20-H20-SUM(M20:AV20)</f>
         <v/>
       </c>
       <c r="AZ20" s="25">
-        <f>IF(I20=0,"",AX20/I20)</f>
+        <f>IF(I20=0,"",(H20+SUM(M20:AV20))/I20)</f>
         <v/>
       </c>
       <c r="BA20" s="26" t="n"/>
@@ -2506,15 +2541,15 @@
       <c r="AV21" s="21" t="n"/>
       <c r="AW21" s="21" t="n"/>
       <c r="AX21" s="24">
-        <f>SUM(M21:AV21)</f>
+        <f>H21+SUM(M21:AV21)</f>
         <v/>
       </c>
       <c r="AY21" s="24">
-        <f>I21-AX21</f>
+        <f>I21-H21-SUM(M21:AV21)</f>
         <v/>
       </c>
       <c r="AZ21" s="25">
-        <f>IF(I21=0,"",AX21/I21)</f>
+        <f>IF(I21=0,"",(H21+SUM(M21:AV21))/I21)</f>
         <v/>
       </c>
       <c r="BA21" s="26" t="n"/>
@@ -2579,15 +2614,15 @@
       <c r="AV22" s="21" t="n"/>
       <c r="AW22" s="21" t="n"/>
       <c r="AX22" s="24">
-        <f>SUM(M22:AV22)</f>
+        <f>H22+SUM(M22:AV22)</f>
         <v/>
       </c>
       <c r="AY22" s="24">
-        <f>I22-AX22</f>
+        <f>I22-H22-SUM(M22:AV22)</f>
         <v/>
       </c>
       <c r="AZ22" s="25">
-        <f>IF(I22=0,"",AX22/I22)</f>
+        <f>IF(I22=0,"",(H22+SUM(M22:AV22))/I22)</f>
         <v/>
       </c>
       <c r="BA22" s="26" t="n"/>
@@ -2652,15 +2687,15 @@
       <c r="AV23" s="21" t="n"/>
       <c r="AW23" s="21" t="n"/>
       <c r="AX23" s="24">
-        <f>SUM(M23:AV23)</f>
+        <f>H23+SUM(M23:AV23)</f>
         <v/>
       </c>
       <c r="AY23" s="24">
-        <f>I23-AX23</f>
+        <f>I23-H23-SUM(M23:AV23)</f>
         <v/>
       </c>
       <c r="AZ23" s="25">
-        <f>IF(I23=0,"",AX23/I23)</f>
+        <f>IF(I23=0,"",(H23+SUM(M23:AV23))/I23)</f>
         <v/>
       </c>
       <c r="BA23" s="26" t="n"/>
@@ -2725,15 +2760,15 @@
       <c r="AV24" s="21" t="n"/>
       <c r="AW24" s="21" t="n"/>
       <c r="AX24" s="24">
-        <f>SUM(M24:AV24)</f>
+        <f>H24+SUM(M24:AV24)</f>
         <v/>
       </c>
       <c r="AY24" s="24">
-        <f>I24-AX24</f>
+        <f>I24-H24-SUM(M24:AV24)</f>
         <v/>
       </c>
       <c r="AZ24" s="25">
-        <f>IF(I24=0,"",AX24/I24)</f>
+        <f>IF(I24=0,"",(H24+SUM(M24:AV24))/I24)</f>
         <v/>
       </c>
       <c r="BA24" s="26" t="n"/>
@@ -2798,15 +2833,15 @@
       <c r="AV25" s="21" t="n"/>
       <c r="AW25" s="21" t="n"/>
       <c r="AX25" s="24">
-        <f>SUM(M25:AV25)</f>
+        <f>H25+SUM(M25:AV25)</f>
         <v/>
       </c>
       <c r="AY25" s="24">
-        <f>I25-AX25</f>
+        <f>I25-H25-SUM(M25:AV25)</f>
         <v/>
       </c>
       <c r="AZ25" s="25">
-        <f>IF(I25=0,"",AX25/I25)</f>
+        <f>IF(I25=0,"",(H25+SUM(M25:AV25))/I25)</f>
         <v/>
       </c>
       <c r="BA25" s="26" t="n"/>
@@ -2871,15 +2906,15 @@
       <c r="AV26" s="21" t="n"/>
       <c r="AW26" s="21" t="n"/>
       <c r="AX26" s="24">
-        <f>SUM(M26:AV26)</f>
+        <f>H26+SUM(M26:AV26)</f>
         <v/>
       </c>
       <c r="AY26" s="24">
-        <f>I26-AX26</f>
+        <f>I26-H26-SUM(M26:AV26)</f>
         <v/>
       </c>
       <c r="AZ26" s="25">
-        <f>IF(I26=0,"",AX26/I26)</f>
+        <f>IF(I26=0,"",(H26+SUM(M26:AV26))/I26)</f>
         <v/>
       </c>
       <c r="BA26" s="26" t="n"/>
@@ -2944,15 +2979,15 @@
       <c r="AV27" s="21" t="n"/>
       <c r="AW27" s="21" t="n"/>
       <c r="AX27" s="24">
-        <f>SUM(M27:AV27)</f>
+        <f>H27+SUM(M27:AV27)</f>
         <v/>
       </c>
       <c r="AY27" s="24">
-        <f>I27-AX27</f>
+        <f>I27-H27-SUM(M27:AV27)</f>
         <v/>
       </c>
       <c r="AZ27" s="25">
-        <f>IF(I27=0,"",AX27/I27)</f>
+        <f>IF(I27=0,"",(H27+SUM(M27:AV27))/I27)</f>
         <v/>
       </c>
       <c r="BA27" s="26" t="n"/>
@@ -3017,15 +3052,15 @@
       <c r="AV28" s="21" t="n"/>
       <c r="AW28" s="21" t="n"/>
       <c r="AX28" s="24">
-        <f>SUM(M28:AV28)</f>
+        <f>H28+SUM(M28:AV28)</f>
         <v/>
       </c>
       <c r="AY28" s="24">
-        <f>I28-AX28</f>
+        <f>I28-H28-SUM(M28:AV28)</f>
         <v/>
       </c>
       <c r="AZ28" s="25">
-        <f>IF(I28=0,"",AX28/I28)</f>
+        <f>IF(I28=0,"",(H28+SUM(M28:AV28))/I28)</f>
         <v/>
       </c>
       <c r="BA28" s="26" t="n"/>
@@ -3090,15 +3125,15 @@
       <c r="AV29" s="21" t="n"/>
       <c r="AW29" s="21" t="n"/>
       <c r="AX29" s="24">
-        <f>SUM(M29:AV29)</f>
+        <f>H29+SUM(M29:AV29)</f>
         <v/>
       </c>
       <c r="AY29" s="24">
-        <f>I29-AX29</f>
+        <f>I29-H29-SUM(M29:AV29)</f>
         <v/>
       </c>
       <c r="AZ29" s="25">
-        <f>IF(I29=0,"",AX29/I29)</f>
+        <f>IF(I29=0,"",(H29+SUM(M29:AV29))/I29)</f>
         <v/>
       </c>
       <c r="BA29" s="26" t="n"/>
@@ -3163,15 +3198,15 @@
       <c r="AV30" s="21" t="n"/>
       <c r="AW30" s="21" t="n"/>
       <c r="AX30" s="24">
-        <f>SUM(M30:AV30)</f>
+        <f>H30+SUM(M30:AV30)</f>
         <v/>
       </c>
       <c r="AY30" s="24">
-        <f>I30-AX30</f>
+        <f>I30-H30-SUM(M30:AV30)</f>
         <v/>
       </c>
       <c r="AZ30" s="25">
-        <f>IF(I30=0,"",AX30/I30)</f>
+        <f>IF(I30=0,"",(H30+SUM(M30:AV30))/I30)</f>
         <v/>
       </c>
       <c r="BA30" s="26" t="n"/>
@@ -3236,15 +3271,15 @@
       <c r="AV31" s="21" t="n"/>
       <c r="AW31" s="21" t="n"/>
       <c r="AX31" s="24">
-        <f>SUM(M31:AV31)</f>
+        <f>H31+SUM(M31:AV31)</f>
         <v/>
       </c>
       <c r="AY31" s="24">
-        <f>I31-AX31</f>
+        <f>I31-H31-SUM(M31:AV31)</f>
         <v/>
       </c>
       <c r="AZ31" s="25">
-        <f>IF(I31=0,"",AX31/I31)</f>
+        <f>IF(I31=0,"",(H31+SUM(M31:AV31))/I31)</f>
         <v/>
       </c>
       <c r="BA31" s="26" t="n"/>
@@ -3309,15 +3344,15 @@
       <c r="AV32" s="21" t="n"/>
       <c r="AW32" s="21" t="n"/>
       <c r="AX32" s="24">
-        <f>SUM(M32:AV32)</f>
+        <f>H32+SUM(M32:AV32)</f>
         <v/>
       </c>
       <c r="AY32" s="24">
-        <f>I32-AX32</f>
+        <f>I32-H32-SUM(M32:AV32)</f>
         <v/>
       </c>
       <c r="AZ32" s="25">
-        <f>IF(I32=0,"",AX32/I32)</f>
+        <f>IF(I32=0,"",(H32+SUM(M32:AV32))/I32)</f>
         <v/>
       </c>
       <c r="BA32" s="26" t="n"/>
@@ -3382,15 +3417,15 @@
       <c r="AV33" s="21" t="n"/>
       <c r="AW33" s="21" t="n"/>
       <c r="AX33" s="24">
-        <f>SUM(M33:AV33)</f>
+        <f>H33+SUM(M33:AV33)</f>
         <v/>
       </c>
       <c r="AY33" s="24">
-        <f>I33-AX33</f>
+        <f>I33-H33-SUM(M33:AV33)</f>
         <v/>
       </c>
       <c r="AZ33" s="25">
-        <f>IF(I33=0,"",AX33/I33)</f>
+        <f>IF(I33=0,"",(H33+SUM(M33:AV33))/I33)</f>
         <v/>
       </c>
       <c r="BA33" s="26" t="n"/>
@@ -3455,15 +3490,15 @@
       <c r="AV34" s="21" t="n"/>
       <c r="AW34" s="21" t="n"/>
       <c r="AX34" s="24">
-        <f>SUM(M34:AV34)</f>
+        <f>H34+SUM(M34:AV34)</f>
         <v/>
       </c>
       <c r="AY34" s="24">
-        <f>I34-AX34</f>
+        <f>I34-H34-SUM(M34:AV34)</f>
         <v/>
       </c>
       <c r="AZ34" s="25">
-        <f>IF(I34=0,"",AX34/I34)</f>
+        <f>IF(I34=0,"",(H34+SUM(M34:AV34))/I34)</f>
         <v/>
       </c>
       <c r="BA34" s="26" t="n"/>
@@ -3528,15 +3563,15 @@
       <c r="AV35" s="21" t="n"/>
       <c r="AW35" s="21" t="n"/>
       <c r="AX35" s="24">
-        <f>SUM(M35:AV35)</f>
+        <f>H35+SUM(M35:AV35)</f>
         <v/>
       </c>
       <c r="AY35" s="24">
-        <f>I35-AX35</f>
+        <f>I35-H35-SUM(M35:AV35)</f>
         <v/>
       </c>
       <c r="AZ35" s="25">
-        <f>IF(I35=0,"",AX35/I35)</f>
+        <f>IF(I35=0,"",(H35+SUM(M35:AV35))/I35)</f>
         <v/>
       </c>
       <c r="BA35" s="26" t="n"/>
@@ -3601,15 +3636,15 @@
       <c r="AV36" s="21" t="n"/>
       <c r="AW36" s="21" t="n"/>
       <c r="AX36" s="24">
-        <f>SUM(M36:AV36)</f>
+        <f>H36+SUM(M36:AV36)</f>
         <v/>
       </c>
       <c r="AY36" s="24">
-        <f>I36-AX36</f>
+        <f>I36-H36-SUM(M36:AV36)</f>
         <v/>
       </c>
       <c r="AZ36" s="25">
-        <f>IF(I36=0,"",AX36/I36)</f>
+        <f>IF(I36=0,"",(H36+SUM(M36:AV36))/I36)</f>
         <v/>
       </c>
       <c r="BA36" s="26" t="n"/>
@@ -3674,15 +3709,15 @@
       <c r="AV37" s="21" t="n"/>
       <c r="AW37" s="21" t="n"/>
       <c r="AX37" s="24">
-        <f>SUM(M37:AV37)</f>
+        <f>H37+SUM(M37:AV37)</f>
         <v/>
       </c>
       <c r="AY37" s="24">
-        <f>I37-AX37</f>
+        <f>I37-H37-SUM(M37:AV37)</f>
         <v/>
       </c>
       <c r="AZ37" s="25">
-        <f>IF(I37=0,"",AX37/I37)</f>
+        <f>IF(I37=0,"",(H37+SUM(M37:AV37))/I37)</f>
         <v/>
       </c>
       <c r="BA37" s="26" t="n"/>
@@ -3747,15 +3782,15 @@
       <c r="AV38" s="21" t="n"/>
       <c r="AW38" s="21" t="n"/>
       <c r="AX38" s="24">
-        <f>SUM(M38:AV38)</f>
+        <f>H38+SUM(M38:AV38)</f>
         <v/>
       </c>
       <c r="AY38" s="24">
-        <f>I38-AX38</f>
+        <f>I38-H38-SUM(M38:AV38)</f>
         <v/>
       </c>
       <c r="AZ38" s="25">
-        <f>IF(I38=0,"",AX38/I38)</f>
+        <f>IF(I38=0,"",(H38+SUM(M38:AV38))/I38)</f>
         <v/>
       </c>
       <c r="BA38" s="26" t="n"/>
@@ -3820,15 +3855,15 @@
       <c r="AV39" s="21" t="n"/>
       <c r="AW39" s="21" t="n"/>
       <c r="AX39" s="24">
-        <f>SUM(M39:AV39)</f>
+        <f>H39+SUM(M39:AV39)</f>
         <v/>
       </c>
       <c r="AY39" s="24">
-        <f>I39-AX39</f>
+        <f>I39-H39-SUM(M39:AV39)</f>
         <v/>
       </c>
       <c r="AZ39" s="25">
-        <f>IF(I39=0,"",AX39/I39)</f>
+        <f>IF(I39=0,"",(H39+SUM(M39:AV39))/I39)</f>
         <v/>
       </c>
       <c r="BA39" s="26" t="n"/>
@@ -3893,15 +3928,15 @@
       <c r="AV40" s="21" t="n"/>
       <c r="AW40" s="21" t="n"/>
       <c r="AX40" s="24">
-        <f>SUM(M40:AV40)</f>
+        <f>H40+SUM(M40:AV40)</f>
         <v/>
       </c>
       <c r="AY40" s="24">
-        <f>I40-AX40</f>
+        <f>I40-H40-SUM(M40:AV40)</f>
         <v/>
       </c>
       <c r="AZ40" s="25">
-        <f>IF(I40=0,"",AX40/I40)</f>
+        <f>IF(I40=0,"",(H40+SUM(M40:AV40))/I40)</f>
         <v/>
       </c>
       <c r="BA40" s="26" t="n"/>
@@ -3966,15 +4001,15 @@
       <c r="AV41" s="21" t="n"/>
       <c r="AW41" s="21" t="n"/>
       <c r="AX41" s="24">
-        <f>SUM(M41:AV41)</f>
+        <f>H41+SUM(M41:AV41)</f>
         <v/>
       </c>
       <c r="AY41" s="24">
-        <f>I41-AX41</f>
+        <f>I41-H41-SUM(M41:AV41)</f>
         <v/>
       </c>
       <c r="AZ41" s="25">
-        <f>IF(I41=0,"",AX41/I41)</f>
+        <f>IF(I41=0,"",(H41+SUM(M41:AV41))/I41)</f>
         <v/>
       </c>
       <c r="BA41" s="26" t="n"/>
@@ -4039,15 +4074,15 @@
       <c r="AV42" s="21" t="n"/>
       <c r="AW42" s="21" t="n"/>
       <c r="AX42" s="24">
-        <f>SUM(M42:AV42)</f>
+        <f>H42+SUM(M42:AV42)</f>
         <v/>
       </c>
       <c r="AY42" s="24">
-        <f>I42-AX42</f>
+        <f>I42-H42-SUM(M42:AV42)</f>
         <v/>
       </c>
       <c r="AZ42" s="25">
-        <f>IF(I42=0,"",AX42/I42)</f>
+        <f>IF(I42=0,"",(H42+SUM(M42:AV42))/I42)</f>
         <v/>
       </c>
       <c r="BA42" s="26" t="n"/>
@@ -4112,15 +4147,15 @@
       <c r="AV43" s="21" t="n"/>
       <c r="AW43" s="21" t="n"/>
       <c r="AX43" s="24">
-        <f>SUM(M43:AV43)</f>
+        <f>H43+SUM(M43:AV43)</f>
         <v/>
       </c>
       <c r="AY43" s="24">
-        <f>I43-AX43</f>
+        <f>I43-H43-SUM(M43:AV43)</f>
         <v/>
       </c>
       <c r="AZ43" s="25">
-        <f>IF(I43=0,"",AX43/I43)</f>
+        <f>IF(I43=0,"",(H43+SUM(M43:AV43))/I43)</f>
         <v/>
       </c>
       <c r="BA43" s="26" t="n"/>
@@ -4185,15 +4220,15 @@
       <c r="AV44" s="21" t="n"/>
       <c r="AW44" s="21" t="n"/>
       <c r="AX44" s="24">
-        <f>SUM(M44:AV44)</f>
+        <f>H44+SUM(M44:AV44)</f>
         <v/>
       </c>
       <c r="AY44" s="24">
-        <f>I44-AX44</f>
+        <f>I44-H44-SUM(M44:AV44)</f>
         <v/>
       </c>
       <c r="AZ44" s="25">
-        <f>IF(I44=0,"",AX44/I44)</f>
+        <f>IF(I44=0,"",(H44+SUM(M44:AV44))/I44)</f>
         <v/>
       </c>
       <c r="BA44" s="26" t="n"/>
@@ -4258,15 +4293,15 @@
       <c r="AV45" s="21" t="n"/>
       <c r="AW45" s="21" t="n"/>
       <c r="AX45" s="24">
-        <f>SUM(M45:AV45)</f>
+        <f>H45+SUM(M45:AV45)</f>
         <v/>
       </c>
       <c r="AY45" s="24">
-        <f>I45-AX45</f>
+        <f>I45-H45-SUM(M45:AV45)</f>
         <v/>
       </c>
       <c r="AZ45" s="25">
-        <f>IF(I45=0,"",AX45/I45)</f>
+        <f>IF(I45=0,"",(H45+SUM(M45:AV45))/I45)</f>
         <v/>
       </c>
       <c r="BA45" s="26" t="n"/>
@@ -4331,15 +4366,15 @@
       <c r="AV46" s="21" t="n"/>
       <c r="AW46" s="21" t="n"/>
       <c r="AX46" s="24">
-        <f>SUM(M46:AV46)</f>
+        <f>H46+SUM(M46:AV46)</f>
         <v/>
       </c>
       <c r="AY46" s="24">
-        <f>I46-AX46</f>
+        <f>I46-H46-SUM(M46:AV46)</f>
         <v/>
       </c>
       <c r="AZ46" s="25">
-        <f>IF(I46=0,"",AX46/I46)</f>
+        <f>IF(I46=0,"",(H46+SUM(M46:AV46))/I46)</f>
         <v/>
       </c>
       <c r="BA46" s="26" t="n"/>
@@ -4404,15 +4439,15 @@
       <c r="AV47" s="21" t="n"/>
       <c r="AW47" s="21" t="n"/>
       <c r="AX47" s="24">
-        <f>SUM(M47:AV47)</f>
+        <f>H47+SUM(M47:AV47)</f>
         <v/>
       </c>
       <c r="AY47" s="24">
-        <f>I47-AX47</f>
+        <f>I47-H47-SUM(M47:AV47)</f>
         <v/>
       </c>
       <c r="AZ47" s="25">
-        <f>IF(I47=0,"",AX47/I47)</f>
+        <f>IF(I47=0,"",(H47+SUM(M47:AV47))/I47)</f>
         <v/>
       </c>
       <c r="BA47" s="26" t="n"/>
@@ -4477,15 +4512,15 @@
       <c r="AV48" s="21" t="n"/>
       <c r="AW48" s="21" t="n"/>
       <c r="AX48" s="24">
-        <f>SUM(M48:AV48)</f>
+        <f>H48+SUM(M48:AV48)</f>
         <v/>
       </c>
       <c r="AY48" s="24">
-        <f>I48-AX48</f>
+        <f>I48-H48-SUM(M48:AV48)</f>
         <v/>
       </c>
       <c r="AZ48" s="25">
-        <f>IF(I48=0,"",AX48/I48)</f>
+        <f>IF(I48=0,"",(H48+SUM(M48:AV48))/I48)</f>
         <v/>
       </c>
       <c r="BA48" s="26" t="n"/>
@@ -4550,15 +4585,15 @@
       <c r="AV49" s="21" t="n"/>
       <c r="AW49" s="21" t="n"/>
       <c r="AX49" s="24">
-        <f>SUM(M49:AV49)</f>
+        <f>H49+SUM(M49:AV49)</f>
         <v/>
       </c>
       <c r="AY49" s="24">
-        <f>I49-AX49</f>
+        <f>I49-H49-SUM(M49:AV49)</f>
         <v/>
       </c>
       <c r="AZ49" s="25">
-        <f>IF(I49=0,"",AX49/I49)</f>
+        <f>IF(I49=0,"",(H49+SUM(M49:AV49))/I49)</f>
         <v/>
       </c>
       <c r="BA49" s="26" t="n"/>
@@ -4623,15 +4658,15 @@
       <c r="AV50" s="21" t="n"/>
       <c r="AW50" s="21" t="n"/>
       <c r="AX50" s="24">
-        <f>SUM(M50:AV50)</f>
+        <f>H50+SUM(M50:AV50)</f>
         <v/>
       </c>
       <c r="AY50" s="24">
-        <f>I50-AX50</f>
+        <f>I50-H50-SUM(M50:AV50)</f>
         <v/>
       </c>
       <c r="AZ50" s="25">
-        <f>IF(I50=0,"",AX50/I50)</f>
+        <f>IF(I50=0,"",(H50+SUM(M50:AV50))/I50)</f>
         <v/>
       </c>
       <c r="BA50" s="26" t="n"/>
@@ -4696,15 +4731,15 @@
       <c r="AV51" s="21" t="n"/>
       <c r="AW51" s="21" t="n"/>
       <c r="AX51" s="24">
-        <f>SUM(M51:AV51)</f>
+        <f>H51+SUM(M51:AV51)</f>
         <v/>
       </c>
       <c r="AY51" s="24">
-        <f>I51-AX51</f>
+        <f>I51-H51-SUM(M51:AV51)</f>
         <v/>
       </c>
       <c r="AZ51" s="25">
-        <f>IF(I51=0,"",AX51/I51)</f>
+        <f>IF(I51=0,"",(H51+SUM(M51:AV51))/I51)</f>
         <v/>
       </c>
       <c r="BA51" s="26" t="n"/>
